--- a/conformance/cases/xlsx-01-shared-strings.xlsx
+++ b/conformance/cases/xlsx-01-shared-strings.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">start</t>
   </si>
   <si>
-    <t xml:space="preserve">Bắt đầu</t>
+    <t xml:space="preserve">Start</t>
   </si>
   <si>
     <t xml:space="preserve">E1</t>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">edge</t>
   </si>
   <si>
-    <t xml:space="preserve">gửi yêu cầu</t>
+    <t xml:space="preserve">send request</t>
   </si>
   <si>
     <t xml:space="preserve">from=A-1; to=B-1</t>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">task</t>
   </si>
   <si>
-    <t xml:space="preserve">Xử lý</t>
+    <t xml:space="preserve">Process</t>
   </si>
   <si>
     <t xml:space="preserve">E2</t>
@@ -82,7 +82,7 @@
     <t xml:space="preserve">end</t>
   </si>
   <si>
-    <t xml:space="preserve">Xong</t>
+    <t xml:space="preserve">Done</t>
   </si>
 </sst>
 </file>
